--- a/sheets/대금율보/검수/우수 (b1_242_2).xlsx
+++ b/sheets/대금율보/검수/우수 (b1_242_2).xlsx
@@ -4172,11 +4172,7 @@
           <t xml:space="preserve">지만</t>
         </is>
       </c>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H6" s="21"/>
       <c r="I6" s="27"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
@@ -4276,7 +4272,7 @@
       </c>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 林無</t>
         </is>
       </c>
@@ -4684,8 +4680,7 @@
       <c r="D18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-汰
-‹</t>
+汰</t>
         </is>
       </c>
       <c r="E18" s="27" t="inlineStr">
@@ -4693,11 +4688,7 @@
           <t xml:space="preserve">가에</t>
         </is>
       </c>
-      <c r="F18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F18" s="21"/>
       <c r="G18" s="27"/>
       <c r="H18" s="21" t="inlineStr">
         <is>
@@ -4713,8 +4704,7 @@
       <c r="J18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-夾
-‹</t>
+夾</t>
         </is>
       </c>
       <c r="K18" s="27"/>

--- a/sheets/대금율보/검수/우수 (b1_242_2).xlsx
+++ b/sheets/대금율보/검수/우수 (b1_242_2).xlsx
@@ -3977,22 +3977,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="71.43" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="63.84" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="K3" s="24"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="63.84" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="25"/>
@@ -4097,7 +4097,7 @@
       </c>
       <c r="K4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="63.84" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="K5" s="25"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="63.84" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="K6" s="27"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="63.84" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="23" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
       </c>
       <c r="K7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="63.84" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="K8" s="25"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="63.84" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="K9" s="25"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="63.84" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="23" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="K10" s="27"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="63.84" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
       </c>
       <c r="K11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="63.84" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="K12" s="25"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="63.84" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="25"/>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="K13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="63.84" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
       </c>
       <c r="K14" s="27"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="63.84" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="K15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="63.84" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="25"/>
@@ -4629,7 +4629,7 @@
       <c r="J16" s="21"/>
       <c r="K16" s="25"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="63.84" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="25"/>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="K17" s="25"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="63.84" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="27"/>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="K18" s="27"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="63.84" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="22"/>
@@ -4756,7 +4756,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="63.84" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="25"/>
@@ -4805,7 +4805,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="63.84" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="25"/>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="63.84" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="27"/>
@@ -4896,6 +4896,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="56"/>
 </worksheet>
 </file>